--- a/data/trans_dic/P36$pan-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36$pan-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ...</t>
+          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,7; 78,93</t>
+          <t>73,6; 79,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,83; 82,21</t>
+          <t>76,78; 82,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,76; 86,22</t>
+          <t>80,76; 85,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78,03; 82,22</t>
+          <t>77,83; 82,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,48; 86,85</t>
+          <t>82,85; 86,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,2; 90,41</t>
+          <t>86,06; 90,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,75; 80,08</t>
+          <t>76,66; 80,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>80,9; 84,16</t>
+          <t>80,82; 84,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84,71; 88,06</t>
+          <t>84,63; 87,98</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>74,54; 78,69</t>
+          <t>74,5; 78,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,31; 81,92</t>
+          <t>78,1; 82,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,78; 85,01</t>
+          <t>82,0; 85,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,67; 79,76</t>
+          <t>75,43; 79,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>79,97; 83,74</t>
+          <t>79,78; 83,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,83; 87,85</t>
+          <t>84,82; 87,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,69; 78,46</t>
+          <t>75,56; 78,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>79,5; 82,23</t>
+          <t>79,67; 82,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>83,78; 86,06</t>
+          <t>83,87; 86,18</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,22; 79,49</t>
+          <t>72,11; 79,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,37; 84,98</t>
+          <t>76,96; 84,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86,01; 91,72</t>
+          <t>85,66; 91,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70,18; 78,83</t>
+          <t>70,75; 78,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77,48; 85,29</t>
+          <t>77,29; 85,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88,32; 93,12</t>
+          <t>88,44; 93,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,21; 77,78</t>
+          <t>72,2; 77,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>78,31; 83,65</t>
+          <t>78,63; 84,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>88,06; 91,81</t>
+          <t>87,89; 91,57</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,98; 77,87</t>
+          <t>74,85; 77,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,7; 81,52</t>
+          <t>78,64; 81,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83,13; 85,8</t>
+          <t>83,0; 85,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76,77; 79,51</t>
+          <t>76,64; 79,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,64; 84,24</t>
+          <t>81,46; 84,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,55; 88,81</t>
+          <t>86,47; 88,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,3; 78,34</t>
+          <t>76,29; 78,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>80,61; 82,54</t>
+          <t>80,62; 82,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>85,23; 87,05</t>
+          <t>85,21; 86,91</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ...</t>
+          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>757454; 811243</t>
+          <t>756456; 813061</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>747319; 799574</t>
+          <t>746821; 799108</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>607792; 648870</t>
+          <t>607798; 646790</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1024579; 1079705</t>
+          <t>1021960; 1079089</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1101706; 1160046</t>
+          <t>1106634; 1158655</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>856341; 898190</t>
+          <t>854966; 896833</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1796589; 1874661</t>
+          <t>1794491; 1875983</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1867520; 1942864</t>
+          <t>1865731; 1943881</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1479065; 1537562</t>
+          <t>1477667; 1536166</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1261607; 1331799</t>
+          <t>1260857; 1331896</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1535675; 1606535</t>
+          <t>1531622; 1609705</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1696369; 1763237</t>
+          <t>1700920; 1765240</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1199886; 1264637</t>
+          <t>1196006; 1262123</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1403433; 1469456</t>
+          <t>1400113; 1465067</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1684891; 1744963</t>
+          <t>1684685; 1744789</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2481082; 2572077</t>
+          <t>2476859; 2576084</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2954366; 3055533</t>
+          <t>2960607; 3054696</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3401850; 3494385</t>
+          <t>3405379; 3499399</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>396925; 436883</t>
+          <t>396327; 436775</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>371502; 408008</t>
+          <t>369534; 405715</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>470352; 501611</t>
+          <t>468458; 501021</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>334367; 375543</t>
+          <t>337044; 374473</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>354465; 390172</t>
+          <t>353562; 389612</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>485006; 511372</t>
+          <t>485644; 511463</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>740927; 798071</t>
+          <t>740772; 799019</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>734269; 784306</t>
+          <t>737248; 789171</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>965137; 1006313</t>
+          <t>963252; 1003649</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2451660; 2546062</t>
+          <t>2447433; 2549606</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2686844; 2782882</t>
+          <t>2684846; 2783083</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2804402; 2894620</t>
+          <t>2800053; 2887800</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2591023; 2683720</t>
+          <t>2586715; 2685599</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2896717; 2988904</t>
+          <t>2890144; 2984308</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3054356; 3134124</t>
+          <t>3051247; 3131138</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5070013; 5205592</t>
+          <t>5069578; 5206523</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5612155; 5746297</t>
+          <t>5612448; 5752035</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5883234; 6008745</t>
+          <t>5881285; 5998855</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$pan-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36$pan-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,6; 79,11</t>
+          <t>73,68; 78,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,78; 82,16</t>
+          <t>76,86; 82,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,76; 85,95</t>
+          <t>80,76; 86,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77,83; 82,18</t>
+          <t>77,93; 82,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,85; 86,74</t>
+          <t>82,83; 86,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,06; 90,27</t>
+          <t>86,21; 90,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,66; 80,14</t>
+          <t>76,89; 80,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>80,82; 84,21</t>
+          <t>81,01; 84,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84,63; 87,98</t>
+          <t>84,51; 87,95</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>74,5; 78,7</t>
+          <t>74,65; 78,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,1; 82,08</t>
+          <t>78,38; 82,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,0; 85,1</t>
+          <t>81,79; 85,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,43; 79,6</t>
+          <t>75,5; 79,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>79,78; 83,49</t>
+          <t>79,78; 83,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,82; 87,84</t>
+          <t>84,78; 87,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,56; 78,59</t>
+          <t>75,52; 78,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>79,67; 82,2</t>
+          <t>79,72; 82,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>83,87; 86,18</t>
+          <t>83,9; 86,09</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,11; 79,47</t>
+          <t>71,78; 79,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76,96; 84,5</t>
+          <t>76,92; 84,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,66; 91,61</t>
+          <t>85,8; 91,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70,75; 78,6</t>
+          <t>70,63; 78,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77,29; 85,17</t>
+          <t>77,55; 85,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88,44; 93,14</t>
+          <t>88,26; 92,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,2; 77,87</t>
+          <t>72,46; 78,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>78,63; 84,17</t>
+          <t>78,62; 84,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87,89; 91,57</t>
+          <t>87,96; 91,81</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,85; 77,97</t>
+          <t>74,97; 77,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,64; 81,52</t>
+          <t>78,76; 81,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83,0; 85,6</t>
+          <t>82,97; 85,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76,64; 79,57</t>
+          <t>76,73; 79,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,46; 84,11</t>
+          <t>81,61; 84,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,47; 88,73</t>
+          <t>86,6; 88,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,29; 78,35</t>
+          <t>76,21; 78,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>80,62; 82,62</t>
+          <t>80,63; 82,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>85,21; 86,91</t>
+          <t>85,22; 86,96</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>756456; 813061</t>
+          <t>757203; 810832</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>746821; 799108</t>
+          <t>747528; 797803</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>607798; 646790</t>
+          <t>607774; 649633</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1021960; 1079089</t>
+          <t>1023393; 1081028</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1106634; 1158655</t>
+          <t>1106383; 1158505</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>854966; 896833</t>
+          <t>856487; 897245</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1794491; 1875983</t>
+          <t>1799920; 1875900</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1865731; 1943881</t>
+          <t>1870066; 1944335</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1477667; 1536166</t>
+          <t>1475490; 1535656</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1260857; 1331896</t>
+          <t>1263315; 1330622</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1531622; 1609705</t>
+          <t>1537025; 1609200</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1700920; 1765240</t>
+          <t>1696463; 1766606</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1196006; 1262123</t>
+          <t>1197212; 1262256</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1400113; 1465067</t>
+          <t>1400044; 1466691</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1684685; 1744789</t>
+          <t>1683851; 1740440</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2476859; 2576084</t>
+          <t>2475695; 2574326</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2960607; 3054696</t>
+          <t>2962296; 3058476</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3405379; 3499399</t>
+          <t>3406721; 3495747</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>396327; 436775</t>
+          <t>394556; 437186</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>369534; 405715</t>
+          <t>369310; 405357</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>468458; 501021</t>
+          <t>469230; 499963</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>337044; 374473</t>
+          <t>336468; 375331</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>353562; 389612</t>
+          <t>354776; 390449</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>485644; 511463</t>
+          <t>484684; 510340</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>740772; 799019</t>
+          <t>743451; 802758</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>737248; 789171</t>
+          <t>737190; 789354</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>963252; 1003649</t>
+          <t>964113; 1006214</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2447433; 2549606</t>
+          <t>2451542; 2544753</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2684846; 2783083</t>
+          <t>2688812; 2786480</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2800053; 2887800</t>
+          <t>2799118; 2887908</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2586715; 2685599</t>
+          <t>2589879; 2683530</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2890144; 2984308</t>
+          <t>2895694; 2992790</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3051247; 3131138</t>
+          <t>3055859; 3132720</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5069578; 5206523</t>
+          <t>5064353; 5203467</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5612448; 5752035</t>
+          <t>5613672; 5747563</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5881285; 5998855</t>
+          <t>5882007; 6002129</t>
         </is>
       </c>
     </row>
